--- a/events/2026/config/motions.xlsx
+++ b/events/2026/config/motions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\wsw-results\events\2026\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B76AD1-83F8-4D74-9BB7-9FBDC679EB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793D42D0-052F-4945-8811-E8A682CA6CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF5FBE02-F020-4937-8353-2CA7CA3A0870}"/>
   </bookViews>
@@ -413,9 +413,6 @@
     <t>Norman</t>
   </si>
   <si>
-    <t>SÃ©bastien</t>
-  </si>
-  <si>
     <t>Camaret</t>
   </si>
   <si>
@@ -498,6 +495,9 @@
   </si>
   <si>
     <t>Diff</t>
+  </si>
+  <si>
+    <t>Seb</t>
   </si>
 </sst>
 </file>
@@ -1445,16 +1445,16 @@
         <v>4</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -1542,9 +1542,9 @@
       <c r="G3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="5">
-        <f>A3-A2</f>
-        <v>1</v>
+      <c r="J3" s="5" t="str">
+        <f>IF(A3-A2&lt;&gt;1,A3-A2,"")</f>
+        <v/>
       </c>
       <c r="K3" s="5">
         <f t="shared" si="0"/>
@@ -1597,9 +1597,9 @@
       <c r="G4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="5">
-        <f t="shared" ref="J4:J67" si="7">A4-A3</f>
-        <v>1</v>
+      <c r="J4" s="5" t="str">
+        <f t="shared" ref="J4:J67" si="7">IF(A4-A3&lt;&gt;1,A4-A3,"")</f>
+        <v/>
       </c>
       <c r="K4" s="5">
         <f t="shared" si="0"/>
@@ -1649,9 +1649,9 @@
       <c r="H5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J5" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K5" s="5">
         <f t="shared" si="0"/>
@@ -1701,9 +1701,9 @@
       <c r="H6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J6" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K6" s="5">
         <f t="shared" si="0"/>
@@ -1756,9 +1756,9 @@
       <c r="G7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J7" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K7" s="5">
         <f t="shared" si="0"/>
@@ -1808,9 +1808,9 @@
       <c r="G8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J8" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K8" s="5">
         <f t="shared" si="0"/>
@@ -1860,9 +1860,9 @@
       <c r="E9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J9" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="0"/>
@@ -1912,9 +1912,9 @@
       <c r="G10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J10" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K10" s="5">
         <f t="shared" si="0"/>
@@ -1967,9 +1967,9 @@
       <c r="G11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J11" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K11" s="5">
         <f t="shared" si="0"/>
@@ -2019,9 +2019,9 @@
       <c r="G12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J12" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K12" s="5">
         <f t="shared" si="0"/>
@@ -2071,9 +2071,9 @@
       <c r="E13" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J13" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K13" s="5">
         <f t="shared" si="0"/>
@@ -2123,9 +2123,9 @@
       <c r="G14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J14" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J14" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K14" s="5">
         <f t="shared" si="0"/>
@@ -2178,9 +2178,9 @@
       <c r="G15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J15" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K15" s="5">
         <f t="shared" si="0"/>
@@ -2230,9 +2230,9 @@
       <c r="E16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J16" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K16" s="5">
         <f t="shared" si="0"/>
@@ -2282,9 +2282,9 @@
       <c r="G17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J17" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J17" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K17" s="5">
         <f t="shared" si="0"/>
@@ -2334,9 +2334,9 @@
       <c r="G18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J18" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J18" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K18" s="5">
         <f t="shared" si="0"/>
@@ -2389,9 +2389,9 @@
       <c r="G19" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J19" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="0"/>
@@ -2441,9 +2441,9 @@
       <c r="G20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J20" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K20" s="5">
         <f t="shared" si="0"/>
@@ -2493,9 +2493,9 @@
       <c r="G21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J21" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J21" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K21" s="5">
         <f t="shared" si="0"/>
@@ -2548,9 +2548,9 @@
       <c r="G22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J22" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J22" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K22" s="5">
         <f t="shared" si="0"/>
@@ -2603,9 +2603,9 @@
       <c r="G23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J23" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K23" s="5">
         <f t="shared" si="0"/>
@@ -2655,9 +2655,9 @@
       <c r="G24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J24" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J24" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K24" s="5">
         <f t="shared" si="0"/>
@@ -2710,9 +2710,9 @@
       <c r="G25" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J25" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J25" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K25" s="5">
         <f t="shared" si="0"/>
@@ -2762,9 +2762,9 @@
       <c r="G26" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J26" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K26" s="5">
         <f t="shared" si="0"/>
@@ -2814,9 +2814,9 @@
       <c r="G27" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J27" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J27" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K27" s="5">
         <f t="shared" si="0"/>
@@ -2866,9 +2866,9 @@
       <c r="E28" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J28" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K28" s="5">
         <f t="shared" si="0"/>
@@ -2918,9 +2918,9 @@
       <c r="G29" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J29" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J29" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K29" s="5">
         <f t="shared" si="0"/>
@@ -2970,9 +2970,9 @@
       <c r="G30" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J30" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J30" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K30" s="5">
         <f t="shared" si="0"/>
@@ -3022,9 +3022,9 @@
       <c r="G31" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J31" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J31" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K31" s="5">
         <f t="shared" si="0"/>
@@ -3074,9 +3074,9 @@
       <c r="G32" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J32" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J32" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K32" s="5">
         <f t="shared" si="0"/>
@@ -3129,9 +3129,9 @@
       <c r="G33" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J33" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J33" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K33" s="5">
         <f t="shared" si="0"/>
@@ -3181,9 +3181,9 @@
       <c r="G34" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J34" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J34" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K34" s="5">
         <f t="shared" ref="K34:K65" si="9">COUNTA(E34:I34)</f>
@@ -3236,9 +3236,9 @@
       <c r="G35" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J35" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J35" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K35" s="5">
         <f t="shared" si="9"/>
@@ -3288,9 +3288,9 @@
       <c r="G36" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J36" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J36" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K36" s="5">
         <f t="shared" si="9"/>
@@ -3340,9 +3340,9 @@
       <c r="G37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J37" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J37" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K37" s="5">
         <f t="shared" si="9"/>
@@ -3392,9 +3392,9 @@
       <c r="G38" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J38" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J38" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K38" s="5">
         <f t="shared" si="9"/>
@@ -3444,9 +3444,9 @@
       <c r="G39" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J39" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J39" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K39" s="5">
         <f t="shared" si="9"/>
@@ -3496,9 +3496,9 @@
       <c r="G40" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J40" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J40" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K40" s="5">
         <f t="shared" si="9"/>
@@ -3548,9 +3548,9 @@
       <c r="G41" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J41" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J41" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K41" s="5">
         <f t="shared" si="9"/>
@@ -3600,9 +3600,9 @@
       <c r="G42" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J42" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J42" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K42" s="5">
         <f t="shared" si="9"/>
@@ -3652,9 +3652,9 @@
       <c r="E43" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J43" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J43" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K43" s="5">
         <f t="shared" si="9"/>
@@ -3704,9 +3704,9 @@
       <c r="H44" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J44" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J44" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K44" s="5">
         <f t="shared" si="9"/>
@@ -3759,9 +3759,9 @@
       <c r="G45" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J45" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J45" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K45" s="5">
         <f t="shared" si="9"/>
@@ -3814,9 +3814,9 @@
       <c r="I46" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J46" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J46" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K46" s="5">
         <f t="shared" si="9"/>
@@ -3866,9 +3866,9 @@
       <c r="G47" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J47" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J47" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K47" s="5">
         <f t="shared" si="9"/>
@@ -3918,9 +3918,9 @@
       <c r="G48" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J48" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J48" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K48" s="5">
         <f t="shared" si="9"/>
@@ -3970,9 +3970,9 @@
       <c r="G49" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J49" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J49" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K49" s="5">
         <f t="shared" si="9"/>
@@ -4022,9 +4022,9 @@
       <c r="I50" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J50" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J50" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K50" s="5">
         <f t="shared" si="9"/>
@@ -4126,9 +4126,9 @@
       <c r="E52" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J52" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J52" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K52" s="5">
         <f t="shared" si="9"/>
@@ -4178,9 +4178,9 @@
       <c r="E53" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J53" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J53" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K53" s="5">
         <f t="shared" si="9"/>
@@ -4230,9 +4230,9 @@
       <c r="E54" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J54" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J54" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K54" s="5">
         <f t="shared" si="9"/>
@@ -4285,9 +4285,9 @@
       <c r="G55" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J55" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J55" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K55" s="5">
         <f t="shared" si="9"/>
@@ -4340,9 +4340,9 @@
       <c r="G56" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J56" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J56" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="9"/>
@@ -4392,9 +4392,9 @@
       <c r="G57" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J57" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J57" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K57" s="5">
         <f t="shared" si="9"/>
@@ -4447,9 +4447,9 @@
       <c r="H58" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J58" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J58" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K58" s="5">
         <f t="shared" si="9"/>
@@ -4499,9 +4499,9 @@
       <c r="G59" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J59" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J59" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K59" s="5">
         <f t="shared" si="9"/>
@@ -4551,9 +4551,9 @@
       <c r="E60" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J60" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J60" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K60" s="5">
         <f t="shared" si="9"/>
@@ -4606,9 +4606,9 @@
       <c r="G61" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J61" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J61" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K61" s="5">
         <f t="shared" si="9"/>
@@ -4710,9 +4710,9 @@
       <c r="G63" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J63" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J63" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K63" s="5">
         <f t="shared" si="9"/>
@@ -4762,9 +4762,9 @@
       <c r="H64" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J64" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J64" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K64" s="5">
         <f t="shared" si="9"/>
@@ -4814,9 +4814,9 @@
       <c r="G65" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J65" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J65" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K65" s="5">
         <f t="shared" si="9"/>
@@ -4866,12 +4866,12 @@
       <c r="G66" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J66" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J66" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K66" s="5">
-        <f t="shared" ref="K66:K97" si="15">COUNTA(E66:I66)</f>
+        <f t="shared" ref="K66:K86" si="15">COUNTA(E66:I66)</f>
         <v>1</v>
       </c>
       <c r="L66" s="5">
@@ -4918,9 +4918,9 @@
       <c r="G67" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J67" s="5">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="J67" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K67" s="5">
         <f t="shared" si="15"/>
@@ -4970,9 +4970,9 @@
       <c r="G68" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J68" s="5">
-        <f t="shared" ref="J68:J86" si="21">A68-A67</f>
-        <v>1</v>
+      <c r="J68" s="5" t="str">
+        <f t="shared" ref="J68:J86" si="21">IF(A68-A67&lt;&gt;1,A68-A67,"")</f>
+        <v/>
       </c>
       <c r="K68" s="5">
         <f t="shared" si="15"/>
@@ -5022,9 +5022,9 @@
       <c r="G69" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J69" s="5">
+      <c r="J69" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K69" s="5">
         <f t="shared" si="15"/>
@@ -5077,9 +5077,9 @@
       <c r="G70" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J70" s="5">
+      <c r="J70" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K70" s="5">
         <f t="shared" si="15"/>
@@ -5121,17 +5121,17 @@
         <v>9</v>
       </c>
       <c r="C71" t="s">
+        <v>153</v>
+      </c>
+      <c r="D71" t="s">
         <v>125</v>
-      </c>
-      <c r="D71" t="s">
-        <v>126</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J71" s="5">
+      <c r="J71" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K71" s="5">
         <f t="shared" si="15"/>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="M71" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>CAM999SÃ©</v>
+        <v>CAM999SEB</v>
       </c>
       <c r="N71" s="3" t="str">
         <f t="shared" si="16"/>
@@ -5176,14 +5176,14 @@
         <v>84</v>
       </c>
       <c r="D72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J72" s="5">
+      <c r="J72" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K72" s="5">
         <f t="shared" si="15"/>
@@ -5228,7 +5228,7 @@
         <v>58</v>
       </c>
       <c r="D73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>13</v>
@@ -5236,9 +5236,9 @@
       <c r="G73" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J73" s="5">
+      <c r="J73" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K73" s="5">
         <f t="shared" si="15"/>
@@ -5280,17 +5280,17 @@
         <v>9</v>
       </c>
       <c r="C74" t="s">
+        <v>128</v>
+      </c>
+      <c r="D74" t="s">
         <v>129</v>
       </c>
-      <c r="D74" t="s">
-        <v>130</v>
-      </c>
       <c r="G74" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J74" s="5">
+      <c r="J74" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K74" s="5">
         <f t="shared" si="15"/>
@@ -5335,14 +5335,14 @@
         <v>104</v>
       </c>
       <c r="D75" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G75" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J75" s="5">
+      <c r="J75" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K75" s="5">
         <f t="shared" si="15"/>
@@ -5384,17 +5384,17 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
+        <v>131</v>
+      </c>
+      <c r="D76" t="s">
         <v>132</v>
       </c>
-      <c r="D76" t="s">
-        <v>133</v>
-      </c>
       <c r="G76" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J76" s="5">
+      <c r="J76" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K76" s="5">
         <f t="shared" si="15"/>
@@ -5439,14 +5439,14 @@
         <v>96</v>
       </c>
       <c r="D77" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G77" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J77" s="5">
+      <c r="J77" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K77" s="5">
         <f t="shared" si="15"/>
@@ -5488,17 +5488,17 @@
         <v>9</v>
       </c>
       <c r="C78" t="s">
+        <v>134</v>
+      </c>
+      <c r="D78" t="s">
         <v>135</v>
       </c>
-      <c r="D78" t="s">
-        <v>136</v>
-      </c>
       <c r="G78" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J78" s="5">
+      <c r="J78" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K78" s="5">
         <f t="shared" si="15"/>
@@ -5540,17 +5540,17 @@
         <v>9</v>
       </c>
       <c r="C79" t="s">
+        <v>136</v>
+      </c>
+      <c r="D79" t="s">
         <v>137</v>
-      </c>
-      <c r="D79" t="s">
-        <v>138</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J79" s="5">
+      <c r="J79" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K79" s="5">
         <f t="shared" si="15"/>
@@ -5592,17 +5592,17 @@
         <v>9</v>
       </c>
       <c r="C80" t="s">
+        <v>138</v>
+      </c>
+      <c r="D80" t="s">
         <v>139</v>
       </c>
-      <c r="D80" t="s">
-        <v>140</v>
-      </c>
       <c r="G80" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J80" s="5">
+      <c r="J80" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K80" s="5">
         <f t="shared" si="15"/>
@@ -5647,14 +5647,14 @@
         <v>76</v>
       </c>
       <c r="D81" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J81" s="5">
+      <c r="J81" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K81" s="5">
         <f t="shared" si="15"/>
@@ -5696,10 +5696,10 @@
         <v>9</v>
       </c>
       <c r="C82" t="s">
+        <v>141</v>
+      </c>
+      <c r="D82" t="s">
         <v>142</v>
-      </c>
-      <c r="D82" t="s">
-        <v>143</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>13</v>
@@ -5751,17 +5751,17 @@
         <v>9</v>
       </c>
       <c r="C83" t="s">
+        <v>143</v>
+      </c>
+      <c r="D83" t="s">
         <v>144</v>
-      </c>
-      <c r="D83" t="s">
-        <v>145</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J83" s="5">
+      <c r="J83" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K83" s="5">
         <f t="shared" si="15"/>
@@ -5806,14 +5806,14 @@
         <v>90</v>
       </c>
       <c r="D84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G84" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J84" s="5">
+      <c r="J84" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K84" s="5">
         <f t="shared" si="15"/>
@@ -5858,7 +5858,7 @@
         <v>67</v>
       </c>
       <c r="D85" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>12</v>
@@ -5866,9 +5866,9 @@
       <c r="H85" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J85" s="5">
+      <c r="J85" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K85" s="5">
         <f t="shared" si="15"/>
@@ -5910,17 +5910,17 @@
         <v>9</v>
       </c>
       <c r="C86" t="s">
+        <v>147</v>
+      </c>
+      <c r="D86" t="s">
         <v>148</v>
       </c>
-      <c r="D86" t="s">
-        <v>149</v>
-      </c>
       <c r="G86" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J86" s="5">
+      <c r="J86" s="5" t="str">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K86" s="5">
         <f t="shared" si="15"/>

--- a/events/2026/config/motions.xlsx
+++ b/events/2026/config/motions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\wsw-results\events\2026\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793D42D0-052F-4945-8811-E8A682CA6CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928C45FB-A1A4-4893-A90C-F7FD3660B78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF5FBE02-F020-4937-8353-2CA7CA3A0870}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="motions" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">motions!$A$1:$R$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">motions!$A$1:$U$86</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="159">
   <si>
     <t>ID</t>
   </si>
@@ -498,13 +498,28 @@
   </si>
   <si>
     <t>Seb</t>
+  </si>
+  <si>
+    <t>Youth Weekend</t>
+  </si>
+  <si>
+    <t>Entrants Own Motion Mini</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>UKWA Member</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -639,8 +654,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,6 +868,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -999,7 +1041,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1014,13 +1056,25 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1398,25 +1452,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6066FD3-C540-449E-A841-C1FB8B248615}">
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:U86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="10.7109375" style="7" customWidth="1"/>
-    <col min="10" max="11" width="11.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.140625" style="8"/>
+    <col min="8" max="12" width="10.7109375" style="10" customWidth="1"/>
+    <col min="13" max="14" width="11.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="13.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1429,50 +1480,59 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="J1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="K1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="L1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>13</v>
       </c>
@@ -1485,45 +1545,48 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="5">
-        <f t="shared" ref="K2:K33" si="0">COUNTA(E2:I2)</f>
+      <c r="J2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="5">
+        <f t="shared" ref="N2:N33" si="0">COUNTA(H2:L2)</f>
         <v>2</v>
       </c>
-      <c r="L2" s="5">
-        <v>999</v>
-      </c>
-      <c r="M2" s="5" t="str">
-        <f t="shared" ref="M2:M6" si="1">UPPER(_xlfn.CONCAT(LEFT(D2,3),L2,LEFT(C2,3)))</f>
+      <c r="O2" s="5">
+        <v>999</v>
+      </c>
+      <c r="P2" s="5" t="str">
+        <f t="shared" ref="P2:P6" si="1">UPPER(_xlfn.CONCAT(LEFT(D2,3),O2,LEFT(C2,3)))</f>
         <v>GEO999MIC</v>
       </c>
-      <c r="N2" s="3" t="str">
-        <f>IF(E2&lt;&gt;"", _xlfn.CONCAT(E2, " ",IF($K2&gt;1,"5",""),$L2), "")</f>
-        <v/>
-      </c>
-      <c r="O2" s="3" t="str">
-        <f>IF(F2&lt;&gt;"", _xlfn.CONCAT(F2, " ",IF($K2&gt;1,"4",""),$L2), "")</f>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P2" s="3" t="str">
-        <f>IF(G2&lt;&gt;"", _xlfn.CONCAT(G2, " ",IF($K2&gt;1,"3",""),$L2), "")</f>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
       <c r="Q2" s="3" t="str">
-        <f>IF(H2&lt;&gt;"", _xlfn.CONCAT(H2, " ",IF($K2&gt;1,"2",""),$L2), "")</f>
+        <f>IF(H2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"5",""),$O2), "")</f>
         <v/>
       </c>
       <c r="R2" s="3" t="str">
-        <f>IF(I2&lt;&gt;"", _xlfn.CONCAT(I2, " ",IF($K2&gt;1,"1",""),$L2), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <f>IF(I2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"4",""),$O2), "")</f>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S2" s="3" t="str">
+        <f>IF(J2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N2&gt;1,$I2=""),"4",""),$O2), "")</f>
+        <v>Motion 999</v>
+      </c>
+      <c r="T2" s="3" t="str">
+        <f>IF(K2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"2",""),$O2), "")</f>
+        <v/>
+      </c>
+      <c r="U2" s="3" t="str">
+        <f>IF(L2&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N2&gt;1,"1",""),$O2), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>14</v>
       </c>
@@ -1536,49 +1599,55 @@
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="5" t="str">
+      <c r="J3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="5" t="str">
         <f>IF(A3-A2&lt;&gt;1,A3-A2,"")</f>
         <v/>
       </c>
-      <c r="K3" s="5">
+      <c r="N3" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L3" s="5">
-        <v>999</v>
-      </c>
-      <c r="M3" s="5" t="str">
+      <c r="O3" s="5">
+        <v>999</v>
+      </c>
+      <c r="P3" s="5" t="str">
         <f t="shared" si="1"/>
         <v>PET999SIM</v>
       </c>
-      <c r="N3" s="3" t="str">
-        <f t="shared" ref="N3:N34" si="2">IF(E3&lt;&gt;"", _xlfn.CONCAT(E3, " ",IF(COUNTA($E3:$I3)&gt;1,"5",""),$L3), "")</f>
-        <v/>
-      </c>
-      <c r="O3" s="3" t="str">
-        <f t="shared" ref="O3:O34" si="3">IF(F3&lt;&gt;"", _xlfn.CONCAT(F3, " ",IF(COUNTA($E3:$I3)&gt;1,"4",""),$L3), "")</f>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P3" s="3" t="str">
-        <f t="shared" ref="P3:P34" si="4">IF(G3&lt;&gt;"", _xlfn.CONCAT(G3, " ",IF(COUNTA($E3:$I3)&gt;1,"3",""),$L3), "")</f>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
       <c r="Q3" s="3" t="str">
-        <f t="shared" ref="Q3:Q34" si="5">IF(H3&lt;&gt;"", _xlfn.CONCAT(H3, " ",IF(COUNTA($E3:$I3)&gt;1,"2",""),$L3), "")</f>
+        <f t="shared" ref="Q3:Q66" si="2">IF(H3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"5",""),$O3), "")</f>
         <v/>
       </c>
       <c r="R3" s="3" t="str">
-        <f t="shared" ref="R3:R34" si="6">IF(I3&lt;&gt;"", _xlfn.CONCAT(I3, " ",IF(COUNTA($E3:$I3)&gt;1,"1",""),$L3), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" ref="R3:R66" si="3">IF(I3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"4",""),$O3), "")</f>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <f t="shared" ref="S3:S66" si="4">IF(J3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N3&gt;1,$I3=""),"4",""),$O3), "")</f>
+        <v>Motion 999</v>
+      </c>
+      <c r="T3" s="3" t="str">
+        <f t="shared" ref="T3:T66" si="5">IF(K3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"2",""),$O3), "")</f>
+        <v/>
+      </c>
+      <c r="U3" s="3" t="str">
+        <f t="shared" ref="U3:U66" si="6">IF(L3&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N3&gt;1,"1",""),$O3), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>15</v>
       </c>
@@ -1591,49 +1660,55 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="5" t="str">
-        <f t="shared" ref="J4:J67" si="7">IF(A4-A3&lt;&gt;1,A4-A3,"")</f>
-        <v/>
-      </c>
-      <c r="K4" s="5">
+      <c r="J4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="5" t="str">
+        <f t="shared" ref="M4:M67" si="7">IF(A4-A3&lt;&gt;1,A4-A3,"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L4" s="5">
-        <v>999</v>
-      </c>
-      <c r="M4" s="5" t="str">
+      <c r="O4" s="5">
+        <v>999</v>
+      </c>
+      <c r="P4" s="5" t="str">
         <f t="shared" si="1"/>
         <v>GIB999JEN</v>
       </c>
-      <c r="N4" s="3" t="str">
+      <c r="Q4" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O4" s="3" t="str">
+      <c r="R4" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P4" s="3" t="str">
+        <v>Motion 4999</v>
+      </c>
+      <c r="S4" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q4" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T4" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R4" s="3" t="str">
+      <c r="U4" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>16</v>
       </c>
@@ -1646,46 +1721,46 @@
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="K5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="5" t="str">
+      <c r="M5" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K5" s="5">
+      <c r="N5" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L5" s="5">
-        <v>999</v>
-      </c>
-      <c r="M5" s="5" t="str">
+      <c r="O5" s="5">
+        <v>999</v>
+      </c>
+      <c r="P5" s="5" t="str">
         <f t="shared" si="1"/>
         <v>VAS999STA</v>
       </c>
-      <c r="N5" s="3" t="str">
+      <c r="Q5" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O5" s="3" t="str">
+      <c r="R5" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P5" s="3" t="str">
+      <c r="S5" s="3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q5" s="3" t="str">
+      <c r="T5" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>Kiteboard Motion 999</v>
-      </c>
-      <c r="R5" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="U5" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>17</v>
       </c>
@@ -1698,46 +1773,46 @@
       <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="K6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="5" t="str">
+      <c r="M6" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K6" s="5">
+      <c r="N6" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L6" s="5">
-        <v>999</v>
-      </c>
-      <c r="M6" s="5" t="str">
+      <c r="O6" s="5">
+        <v>999</v>
+      </c>
+      <c r="P6" s="5" t="str">
         <f t="shared" si="1"/>
         <v>EIF999AYA</v>
       </c>
-      <c r="N6" s="3" t="str">
+      <c r="Q6" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O6" s="3" t="str">
+      <c r="R6" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P6" s="3" t="str">
+      <c r="S6" s="3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q6" s="3" t="str">
+      <c r="T6" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>Kiteboard Motion 999</v>
-      </c>
-      <c r="R6" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="U6" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>18</v>
       </c>
@@ -1750,49 +1825,55 @@
       <c r="D7" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="5" t="str">
+      <c r="J7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M7" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K7" s="5">
+      <c r="N7" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L7" s="5">
-        <v>999</v>
-      </c>
-      <c r="M7" s="5" t="str">
-        <f>UPPER(_xlfn.CONCAT(LEFT(D7,3),L7,LEFT(C7,3)))</f>
+      <c r="O7" s="5">
+        <v>999</v>
+      </c>
+      <c r="P7" s="5" t="str">
+        <f>UPPER(_xlfn.CONCAT(LEFT(D7,3),O7,LEFT(C7,3)))</f>
         <v>CHI999DYL</v>
       </c>
-      <c r="N7" s="3" t="str">
+      <c r="Q7" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O7" s="3" t="str">
+      <c r="R7" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P7" s="3" t="str">
+        <v>Motion 4999</v>
+      </c>
+      <c r="S7" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q7" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T7" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R7" s="3" t="str">
+      <c r="U7" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>19</v>
       </c>
@@ -1805,46 +1886,49 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="5" t="str">
+      <c r="F8" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K8" s="5">
+      <c r="N8" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L8" s="5">
-        <v>999</v>
-      </c>
-      <c r="M8" s="5" t="str">
-        <f t="shared" ref="M8:M71" si="8">UPPER(_xlfn.CONCAT(LEFT(D8,3),L8,LEFT(C8,3)))</f>
+      <c r="O8" s="5">
+        <v>999</v>
+      </c>
+      <c r="P8" s="5" t="str">
+        <f t="shared" ref="P8:P71" si="8">UPPER(_xlfn.CONCAT(LEFT(D8,3),O8,LEFT(C8,3)))</f>
         <v>HEN999RIC</v>
       </c>
-      <c r="N8" s="3" t="str">
+      <c r="Q8" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O8" s="3" t="str">
+      <c r="R8" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P8" s="3" t="str">
+      <c r="S8" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q8" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T8" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R8" s="3" t="str">
+      <c r="U8" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20</v>
       </c>
@@ -1857,46 +1941,52 @@
       <c r="D9" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G9" s="12">
+        <v>940</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="5" t="str">
+      <c r="M9" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K9" s="5">
+      <c r="N9" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L9" s="5">
-        <v>999</v>
-      </c>
-      <c r="M9" s="5" t="str">
+      <c r="O9" s="11">
+        <v>940</v>
+      </c>
+      <c r="P9" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>DIC999ROD</v>
-      </c>
-      <c r="N9" s="3" t="str">
+        <v>DIC940ROD</v>
+      </c>
+      <c r="Q9" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O9" s="3" t="str">
+        <v>Motion 940</v>
+      </c>
+      <c r="R9" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P9" s="3" t="str">
+      <c r="S9" s="3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q9" s="3" t="str">
+      <c r="T9" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R9" s="3" t="str">
+      <c r="U9" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21</v>
       </c>
@@ -1909,46 +1999,49 @@
       <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="5" t="str">
+      <c r="F10" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K10" s="5">
+      <c r="N10" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L10" s="5">
-        <v>999</v>
-      </c>
-      <c r="M10" s="5" t="str">
+      <c r="O10" s="5">
+        <v>999</v>
+      </c>
+      <c r="P10" s="5" t="str">
         <f t="shared" si="8"/>
         <v>DE 999JEA</v>
       </c>
-      <c r="N10" s="3" t="str">
+      <c r="Q10" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O10" s="3" t="str">
+      <c r="R10" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P10" s="3" t="str">
+      <c r="S10" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q10" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T10" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R10" s="3" t="str">
+      <c r="U10" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>22</v>
       </c>
@@ -1961,49 +2054,52 @@
       <c r="D11" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="5" t="str">
+      <c r="J11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K11" s="5">
+      <c r="N11" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L11" s="5">
-        <v>999</v>
-      </c>
-      <c r="M11" s="5" t="str">
+      <c r="O11" s="5">
+        <v>999</v>
+      </c>
+      <c r="P11" s="5" t="str">
         <f t="shared" si="8"/>
         <v>DUD999RIC</v>
       </c>
-      <c r="N11" s="3" t="str">
+      <c r="Q11" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O11" s="3" t="str">
+      <c r="R11" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P11" s="3" t="str">
+        <v>Motion 4999</v>
+      </c>
+      <c r="S11" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q11" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T11" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R11" s="3" t="str">
+      <c r="U11" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>23</v>
       </c>
@@ -2016,46 +2112,49 @@
       <c r="D12" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="5" t="str">
+      <c r="F12" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M12" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K12" s="5">
+      <c r="N12" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L12" s="5">
-        <v>999</v>
-      </c>
-      <c r="M12" s="5" t="str">
+      <c r="O12" s="5">
+        <v>999</v>
+      </c>
+      <c r="P12" s="5" t="str">
         <f t="shared" si="8"/>
         <v>MEY999BEN</v>
       </c>
-      <c r="N12" s="3" t="str">
+      <c r="Q12" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O12" s="3" t="str">
+      <c r="R12" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P12" s="3" t="str">
+      <c r="S12" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q12" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T12" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R12" s="3" t="str">
+      <c r="U12" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>24</v>
       </c>
@@ -2068,46 +2167,49 @@
       <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="5" t="str">
+      <c r="M13" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K13" s="5">
+      <c r="N13" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L13" s="5">
-        <v>999</v>
-      </c>
-      <c r="M13" s="5" t="str">
+      <c r="O13" s="5">
+        <v>999</v>
+      </c>
+      <c r="P13" s="5" t="str">
         <f t="shared" si="8"/>
         <v>MIL999JEZ</v>
       </c>
-      <c r="N13" s="3" t="str">
+      <c r="Q13" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O13" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="R13" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P13" s="3" t="str">
+      <c r="S13" s="3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q13" s="3" t="str">
+      <c r="T13" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R13" s="3" t="str">
+      <c r="U13" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25</v>
       </c>
@@ -2120,46 +2222,49 @@
       <c r="D14" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="5" t="str">
+      <c r="F14" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K14" s="5">
+      <c r="N14" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L14" s="5">
-        <v>999</v>
-      </c>
-      <c r="M14" s="5" t="str">
+      <c r="O14" s="5">
+        <v>999</v>
+      </c>
+      <c r="P14" s="5" t="str">
         <f t="shared" si="8"/>
         <v>REE999MAR</v>
       </c>
-      <c r="N14" s="3" t="str">
+      <c r="Q14" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O14" s="3" t="str">
+      <c r="R14" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P14" s="3" t="str">
+      <c r="S14" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q14" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T14" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R14" s="3" t="str">
+      <c r="U14" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26</v>
       </c>
@@ -2172,49 +2277,52 @@
       <c r="D15" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="5" t="str">
+      <c r="J15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K15" s="5">
+      <c r="N15" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L15" s="5">
-        <v>999</v>
-      </c>
-      <c r="M15" s="5" t="str">
+      <c r="O15" s="5">
+        <v>999</v>
+      </c>
+      <c r="P15" s="5" t="str">
         <f t="shared" si="8"/>
         <v>LON999ROB</v>
       </c>
-      <c r="N15" s="3" t="str">
+      <c r="Q15" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O15" s="3" t="str">
+      <c r="R15" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P15" s="3" t="str">
+        <v>Motion 4999</v>
+      </c>
+      <c r="S15" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q15" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T15" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R15" s="3" t="str">
+      <c r="U15" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>27</v>
       </c>
@@ -2227,46 +2335,49 @@
       <c r="D16" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="5" t="str">
+      <c r="M16" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K16" s="5">
+      <c r="N16" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L16" s="5">
-        <v>999</v>
-      </c>
-      <c r="M16" s="5" t="str">
+      <c r="O16" s="5">
+        <v>999</v>
+      </c>
+      <c r="P16" s="5" t="str">
         <f t="shared" si="8"/>
         <v>ROG999KAT</v>
       </c>
-      <c r="N16" s="3" t="str">
+      <c r="Q16" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O16" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="R16" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P16" s="3" t="str">
+      <c r="S16" s="3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q16" s="3" t="str">
+      <c r="T16" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R16" s="3" t="str">
+      <c r="U16" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>28</v>
       </c>
@@ -2279,46 +2390,49 @@
       <c r="D17" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="5" t="str">
+      <c r="F17" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K17" s="5">
+      <c r="N17" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L17" s="5">
-        <v>999</v>
-      </c>
-      <c r="M17" s="5" t="str">
+      <c r="O17" s="5">
+        <v>999</v>
+      </c>
+      <c r="P17" s="5" t="str">
         <f t="shared" si="8"/>
         <v>SMI999BAR</v>
       </c>
-      <c r="N17" s="3" t="str">
+      <c r="Q17" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O17" s="3" t="str">
+      <c r="R17" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P17" s="3" t="str">
+      <c r="S17" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q17" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T17" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R17" s="3" t="str">
+      <c r="U17" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>29</v>
       </c>
@@ -2331,46 +2445,49 @@
       <c r="D18" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="5" t="str">
+      <c r="F18" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K18" s="5">
+      <c r="N18" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L18" s="5">
-        <v>999</v>
-      </c>
-      <c r="M18" s="5" t="str">
+      <c r="O18" s="5">
+        <v>999</v>
+      </c>
+      <c r="P18" s="5" t="str">
         <f t="shared" si="8"/>
         <v>CRO999RIC</v>
       </c>
-      <c r="N18" s="3" t="str">
+      <c r="Q18" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O18" s="3" t="str">
+      <c r="R18" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P18" s="3" t="str">
+      <c r="S18" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q18" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T18" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R18" s="3" t="str">
+      <c r="U18" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>30</v>
       </c>
@@ -2383,49 +2500,52 @@
       <c r="D19" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="5" t="str">
+      <c r="J19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M19" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K19" s="5">
+      <c r="N19" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L19" s="5">
-        <v>999</v>
-      </c>
-      <c r="M19" s="5" t="str">
+      <c r="O19" s="5">
+        <v>999</v>
+      </c>
+      <c r="P19" s="5" t="str">
         <f t="shared" si="8"/>
         <v>CRO999PET</v>
       </c>
-      <c r="N19" s="3" t="str">
+      <c r="Q19" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O19" s="3" t="str">
+      <c r="R19" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P19" s="3" t="str">
+        <v>Motion 4999</v>
+      </c>
+      <c r="S19" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q19" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T19" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R19" s="3" t="str">
+      <c r="U19" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>31</v>
       </c>
@@ -2438,46 +2558,49 @@
       <c r="D20" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="5" t="str">
+      <c r="F20" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M20" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K20" s="5">
+      <c r="N20" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L20" s="5">
-        <v>999</v>
-      </c>
-      <c r="M20" s="5" t="str">
+      <c r="O20" s="5">
+        <v>999</v>
+      </c>
+      <c r="P20" s="5" t="str">
         <f t="shared" si="8"/>
         <v>BAR999SIM</v>
       </c>
-      <c r="N20" s="3" t="str">
+      <c r="Q20" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O20" s="3" t="str">
+      <c r="R20" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P20" s="3" t="str">
+      <c r="S20" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q20" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T20" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R20" s="3" t="str">
+      <c r="U20" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>32</v>
       </c>
@@ -2490,46 +2613,49 @@
       <c r="D21" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" s="5" t="str">
+      <c r="F21" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M21" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K21" s="5">
+      <c r="N21" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L21" s="5">
-        <v>999</v>
-      </c>
-      <c r="M21" s="5" t="str">
+      <c r="O21" s="5">
+        <v>999</v>
+      </c>
+      <c r="P21" s="5" t="str">
         <f t="shared" si="8"/>
         <v>MAY999SCO</v>
       </c>
-      <c r="N21" s="3" t="str">
+      <c r="Q21" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O21" s="3" t="str">
+      <c r="R21" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P21" s="3" t="str">
+      <c r="S21" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q21" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T21" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R21" s="3" t="str">
+      <c r="U21" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>33</v>
       </c>
@@ -2542,49 +2668,52 @@
       <c r="D22" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I22" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J22" s="5" t="str">
+      <c r="J22" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M22" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K22" s="5">
+      <c r="N22" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L22" s="5">
-        <v>999</v>
-      </c>
-      <c r="M22" s="5" t="str">
+      <c r="O22" s="5">
+        <v>999</v>
+      </c>
+      <c r="P22" s="5" t="str">
         <f t="shared" si="8"/>
         <v>ILI999NIK</v>
       </c>
-      <c r="N22" s="3" t="str">
+      <c r="Q22" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O22" s="3" t="str">
+      <c r="R22" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P22" s="3" t="str">
+        <v>Motion 4999</v>
+      </c>
+      <c r="S22" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q22" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T22" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R22" s="3" t="str">
+      <c r="U22" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>34</v>
       </c>
@@ -2597,49 +2726,52 @@
       <c r="D23" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J23" s="5" t="str">
+      <c r="J23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K23" s="5">
+      <c r="N23" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L23" s="5">
-        <v>999</v>
-      </c>
-      <c r="M23" s="5" t="str">
+      <c r="O23" s="5">
+        <v>999</v>
+      </c>
+      <c r="P23" s="5" t="str">
         <f t="shared" si="8"/>
         <v>ING999MAR</v>
       </c>
-      <c r="N23" s="3" t="str">
+      <c r="Q23" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O23" s="3" t="str">
+      <c r="R23" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P23" s="3" t="str">
+        <v>Motion 4999</v>
+      </c>
+      <c r="S23" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q23" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T23" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R23" s="3" t="str">
+      <c r="U23" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>35</v>
       </c>
@@ -2652,46 +2784,49 @@
       <c r="D24" t="s">
         <v>55</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" s="5" t="str">
+      <c r="F24" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M24" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K24" s="5">
+      <c r="N24" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L24" s="5">
-        <v>999</v>
-      </c>
-      <c r="M24" s="5" t="str">
+      <c r="O24" s="5">
+        <v>999</v>
+      </c>
+      <c r="P24" s="5" t="str">
         <f t="shared" si="8"/>
         <v>ING999JON</v>
       </c>
-      <c r="N24" s="3" t="str">
+      <c r="Q24" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O24" s="3" t="str">
+      <c r="R24" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P24" s="3" t="str">
+      <c r="S24" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q24" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T24" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R24" s="3" t="str">
+      <c r="U24" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>36</v>
       </c>
@@ -2704,49 +2839,52 @@
       <c r="D25" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J25" s="5" t="str">
+      <c r="J25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K25" s="5">
+      <c r="N25" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L25" s="5">
-        <v>999</v>
-      </c>
-      <c r="M25" s="5" t="str">
+      <c r="O25" s="5">
+        <v>999</v>
+      </c>
+      <c r="P25" s="5" t="str">
         <f t="shared" si="8"/>
         <v>SAL999MAR</v>
       </c>
-      <c r="N25" s="3" t="str">
+      <c r="Q25" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O25" s="3" t="str">
+      <c r="R25" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P25" s="3" t="str">
+        <v>Motion 4999</v>
+      </c>
+      <c r="S25" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q25" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T25" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R25" s="3" t="str">
+      <c r="U25" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>37</v>
       </c>
@@ -2759,46 +2897,49 @@
       <c r="D26" t="s">
         <v>59</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J26" s="5" t="str">
+      <c r="F26" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M26" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K26" s="5">
+      <c r="N26" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L26" s="5">
-        <v>999</v>
-      </c>
-      <c r="M26" s="5" t="str">
+      <c r="O26" s="5">
+        <v>999</v>
+      </c>
+      <c r="P26" s="5" t="str">
         <f t="shared" si="8"/>
         <v>OWE999AND</v>
       </c>
-      <c r="N26" s="3" t="str">
+      <c r="Q26" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O26" s="3" t="str">
+      <c r="R26" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P26" s="3" t="str">
+      <c r="S26" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q26" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T26" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R26" s="3" t="str">
+      <c r="U26" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>38</v>
       </c>
@@ -2811,46 +2952,49 @@
       <c r="D27" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J27" s="5" t="str">
+      <c r="F27" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K27" s="5">
+      <c r="N27" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L27" s="5">
-        <v>999</v>
-      </c>
-      <c r="M27" s="5" t="str">
+      <c r="O27" s="5">
+        <v>999</v>
+      </c>
+      <c r="P27" s="5" t="str">
         <f t="shared" si="8"/>
         <v>LIL999MAT</v>
       </c>
-      <c r="N27" s="3" t="str">
+      <c r="Q27" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O27" s="3" t="str">
+      <c r="R27" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P27" s="3" t="str">
+      <c r="S27" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q27" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T27" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R27" s="3" t="str">
+      <c r="U27" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>39</v>
       </c>
@@ -2863,46 +3007,53 @@
       <c r="D28" t="s">
         <v>63</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="F28" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G28" s="8">
+        <v>707</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="5" t="str">
+      <c r="M28" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K28" s="5">
+      <c r="N28" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L28" s="5">
-        <v>999</v>
-      </c>
-      <c r="M28" s="5" t="str">
+      <c r="O28" s="11">
+        <f>G28</f>
+        <v>707</v>
+      </c>
+      <c r="P28" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>GOR999DEN</v>
-      </c>
-      <c r="N28" s="3" t="str">
+        <v>GOR707DEN</v>
+      </c>
+      <c r="Q28" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O28" s="3" t="str">
+        <v>Motion 707</v>
+      </c>
+      <c r="R28" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P28" s="3" t="str">
+      <c r="S28" s="3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q28" s="3" t="str">
+      <c r="T28" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R28" s="3" t="str">
+      <c r="U28" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>40</v>
       </c>
@@ -2915,46 +3066,49 @@
       <c r="D29" t="s">
         <v>64</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J29" s="5" t="str">
+      <c r="F29" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M29" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K29" s="5">
+      <c r="N29" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L29" s="5">
-        <v>999</v>
-      </c>
-      <c r="M29" s="5" t="str">
+      <c r="O29" s="5">
+        <v>999</v>
+      </c>
+      <c r="P29" s="5" t="str">
         <f t="shared" si="8"/>
         <v>HAR999SCO</v>
       </c>
-      <c r="N29" s="3" t="str">
+      <c r="Q29" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O29" s="3" t="str">
+      <c r="R29" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P29" s="3" t="str">
+      <c r="S29" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q29" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T29" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R29" s="3" t="str">
+      <c r="U29" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>41</v>
       </c>
@@ -2967,46 +3121,49 @@
       <c r="D30" t="s">
         <v>64</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J30" s="5" t="str">
+      <c r="F30" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M30" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K30" s="5">
+      <c r="N30" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L30" s="5">
-        <v>999</v>
-      </c>
-      <c r="M30" s="5" t="str">
+      <c r="O30" s="5">
+        <v>999</v>
+      </c>
+      <c r="P30" s="5" t="str">
         <f t="shared" si="8"/>
         <v>HAR999SIA</v>
       </c>
-      <c r="N30" s="3" t="str">
+      <c r="Q30" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O30" s="3" t="str">
+      <c r="R30" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P30" s="3" t="str">
+      <c r="S30" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q30" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T30" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R30" s="3" t="str">
+      <c r="U30" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>42</v>
       </c>
@@ -3019,46 +3176,49 @@
       <c r="D31" t="s">
         <v>36</v>
       </c>
-      <c r="G31" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J31" s="5" t="str">
+      <c r="F31" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M31" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K31" s="5">
+      <c r="N31" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L31" s="5">
-        <v>999</v>
-      </c>
-      <c r="M31" s="5" t="str">
+      <c r="O31" s="5">
+        <v>999</v>
+      </c>
+      <c r="P31" s="5" t="str">
         <f t="shared" si="8"/>
         <v>MEY999NEI</v>
       </c>
-      <c r="N31" s="3" t="str">
+      <c r="Q31" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O31" s="3" t="str">
+      <c r="R31" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P31" s="3" t="str">
+      <c r="S31" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q31" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T31" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R31" s="3" t="str">
+      <c r="U31" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>43</v>
       </c>
@@ -3071,46 +3231,49 @@
       <c r="D32" t="s">
         <v>68</v>
       </c>
-      <c r="G32" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J32" s="5" t="str">
+      <c r="F32" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M32" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K32" s="5">
+      <c r="N32" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L32" s="5">
-        <v>999</v>
-      </c>
-      <c r="M32" s="5" t="str">
+      <c r="O32" s="5">
+        <v>999</v>
+      </c>
+      <c r="P32" s="5" t="str">
         <f t="shared" si="8"/>
         <v>WAT999STE</v>
       </c>
-      <c r="N32" s="3" t="str">
+      <c r="Q32" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O32" s="3" t="str">
+      <c r="R32" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P32" s="3" t="str">
+      <c r="S32" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q32" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T32" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R32" s="3" t="str">
+      <c r="U32" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>44</v>
       </c>
@@ -3123,49 +3286,52 @@
       <c r="D33" t="s">
         <v>70</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J33" s="5" t="str">
+      <c r="J33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M33" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K33" s="5">
+      <c r="N33" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="L33" s="5">
-        <v>999</v>
-      </c>
-      <c r="M33" s="5" t="str">
+      <c r="O33" s="5">
+        <v>999</v>
+      </c>
+      <c r="P33" s="5" t="str">
         <f t="shared" si="8"/>
         <v>LOR999BRE</v>
       </c>
-      <c r="N33" s="3" t="str">
+      <c r="Q33" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O33" s="3" t="str">
+      <c r="R33" s="3" t="str">
         <f t="shared" si="3"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P33" s="3" t="str">
+        <v>Motion 4999</v>
+      </c>
+      <c r="S33" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q33" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T33" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R33" s="3" t="str">
+      <c r="U33" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>45</v>
       </c>
@@ -3178,46 +3344,49 @@
       <c r="D34" t="s">
         <v>70</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" s="5" t="str">
+      <c r="F34" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M34" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K34" s="5">
-        <f t="shared" ref="K34:K65" si="9">COUNTA(E34:I34)</f>
+      <c r="N34" s="5">
+        <f t="shared" ref="N34:N65" si="9">COUNTA(H34:L34)</f>
         <v>1</v>
       </c>
-      <c r="L34" s="5">
-        <v>999</v>
-      </c>
-      <c r="M34" s="5" t="str">
+      <c r="O34" s="5">
+        <v>999</v>
+      </c>
+      <c r="P34" s="5" t="str">
         <f t="shared" si="8"/>
         <v>LOR999FRA</v>
       </c>
-      <c r="N34" s="3" t="str">
+      <c r="Q34" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O34" s="3" t="str">
+      <c r="R34" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P34" s="3" t="str">
+      <c r="S34" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q34" s="3" t="str">
+        <v>Motion 999</v>
+      </c>
+      <c r="T34" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="R34" s="3" t="str">
+      <c r="U34" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>46</v>
       </c>
@@ -3230,49 +3399,52 @@
       <c r="D35" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I35" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J35" s="5" t="str">
+      <c r="J35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M35" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K35" s="5">
+      <c r="N35" s="5">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="L35" s="5">
-        <v>999</v>
-      </c>
-      <c r="M35" s="5" t="str">
+      <c r="O35" s="5">
+        <v>999</v>
+      </c>
+      <c r="P35" s="5" t="str">
         <f t="shared" si="8"/>
         <v>DIC999FIN</v>
       </c>
-      <c r="N35" s="3" t="str">
-        <f t="shared" ref="N35:N66" si="10">IF(E35&lt;&gt;"", _xlfn.CONCAT(E35, " ",IF(COUNTA($E35:$I35)&gt;1,"5",""),$L35), "")</f>
-        <v/>
-      </c>
-      <c r="O35" s="3" t="str">
-        <f t="shared" ref="O35:O66" si="11">IF(F35&lt;&gt;"", _xlfn.CONCAT(F35, " ",IF(COUNTA($E35:$I35)&gt;1,"4",""),$L35), "")</f>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P35" s="3" t="str">
-        <f t="shared" ref="P35:P66" si="12">IF(G35&lt;&gt;"", _xlfn.CONCAT(G35, " ",IF(COUNTA($E35:$I35)&gt;1,"3",""),$L35), "")</f>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
       <c r="Q35" s="3" t="str">
-        <f t="shared" ref="Q35:Q66" si="13">IF(H35&lt;&gt;"", _xlfn.CONCAT(H35, " ",IF(COUNTA($E35:$I35)&gt;1,"2",""),$L35), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R35" s="3" t="str">
-        <f t="shared" ref="R35:R66" si="14">IF(I35&lt;&gt;"", _xlfn.CONCAT(I35, " ",IF(COUNTA($E35:$I35)&gt;1,"1",""),$L35), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S35" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T35" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U35" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>47</v>
       </c>
@@ -3285,46 +3457,53 @@
       <c r="D36" t="s">
         <v>73</v>
       </c>
-      <c r="G36" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J36" s="5" t="str">
+      <c r="F36" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G36" s="12">
+        <v>623</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M36" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K36" s="5">
+      <c r="N36" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L36" s="5">
-        <v>999</v>
-      </c>
-      <c r="M36" s="5" t="str">
+      <c r="O36" s="11">
+        <f>G36</f>
+        <v>623</v>
+      </c>
+      <c r="P36" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>FUL999GEO</v>
-      </c>
-      <c r="N36" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O36" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P36" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
+        <v>FUL623GEO</v>
       </c>
       <c r="Q36" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R36" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S36" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 623</v>
+      </c>
+      <c r="T36" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U36" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>48</v>
       </c>
@@ -3337,46 +3516,49 @@
       <c r="D37" t="s">
         <v>75</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J37" s="5" t="str">
+      <c r="F37" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M37" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K37" s="5">
+      <c r="N37" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L37" s="5">
-        <v>999</v>
-      </c>
-      <c r="M37" s="5" t="str">
+      <c r="O37" s="5">
+        <v>999</v>
+      </c>
+      <c r="P37" s="5" t="str">
         <f t="shared" si="8"/>
         <v>SPA999BOB</v>
       </c>
-      <c r="N37" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O37" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P37" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q37" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R37" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S37" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T37" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U37" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>49</v>
       </c>
@@ -3389,46 +3571,49 @@
       <c r="D38" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J38" s="5" t="str">
+      <c r="F38" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M38" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K38" s="5">
+      <c r="N38" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L38" s="5">
-        <v>999</v>
-      </c>
-      <c r="M38" s="5" t="str">
+      <c r="O38" s="5">
+        <v>999</v>
+      </c>
+      <c r="P38" s="5" t="str">
         <f t="shared" si="8"/>
         <v>ARN999PAU</v>
       </c>
-      <c r="N38" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O38" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P38" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q38" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R38" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S38" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T38" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U38" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>50</v>
       </c>
@@ -3441,46 +3626,49 @@
       <c r="D39" t="s">
         <v>78</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J39" s="5" t="str">
+      <c r="F39" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M39" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K39" s="5">
+      <c r="N39" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L39" s="5">
-        <v>999</v>
-      </c>
-      <c r="M39" s="5" t="str">
+      <c r="O39" s="5">
+        <v>999</v>
+      </c>
+      <c r="P39" s="5" t="str">
         <f t="shared" si="8"/>
         <v>THO999STE</v>
       </c>
-      <c r="N39" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O39" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P39" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q39" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R39" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S39" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T39" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U39" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>51</v>
       </c>
@@ -3493,46 +3681,49 @@
       <c r="D40" t="s">
         <v>80</v>
       </c>
-      <c r="G40" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J40" s="5" t="str">
+      <c r="F40" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M40" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K40" s="5">
+      <c r="N40" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L40" s="5">
-        <v>999</v>
-      </c>
-      <c r="M40" s="5" t="str">
+      <c r="O40" s="5">
+        <v>999</v>
+      </c>
+      <c r="P40" s="5" t="str">
         <f t="shared" si="8"/>
         <v>WAT999JOE</v>
       </c>
-      <c r="N40" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O40" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P40" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q40" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R40" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S40" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T40" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U40" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>52</v>
       </c>
@@ -3545,46 +3736,49 @@
       <c r="D41" t="s">
         <v>82</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J41" s="5" t="str">
+      <c r="F41" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M41" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K41" s="5">
+      <c r="N41" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L41" s="5">
-        <v>999</v>
-      </c>
-      <c r="M41" s="5" t="str">
+      <c r="O41" s="5">
+        <v>999</v>
+      </c>
+      <c r="P41" s="5" t="str">
         <f t="shared" si="8"/>
         <v>DAF999CHR</v>
       </c>
-      <c r="N41" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O41" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P41" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q41" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R41" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S41" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T41" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U41" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>53</v>
       </c>
@@ -3597,46 +3791,49 @@
       <c r="D42" t="s">
         <v>83</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J42" s="5" t="str">
+      <c r="F42" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M42" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K42" s="5">
+      <c r="N42" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L42" s="5">
-        <v>999</v>
-      </c>
-      <c r="M42" s="5" t="str">
+      <c r="O42" s="5">
+        <v>999</v>
+      </c>
+      <c r="P42" s="5" t="str">
         <f t="shared" si="8"/>
         <v>WIL999JON</v>
       </c>
-      <c r="N42" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O42" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P42" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q42" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R42" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S42" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T42" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U42" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>54</v>
       </c>
@@ -3649,46 +3846,49 @@
       <c r="D43" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="F43" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J43" s="5" t="str">
+      <c r="M43" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K43" s="5">
+      <c r="N43" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L43" s="5">
-        <v>999</v>
-      </c>
-      <c r="M43" s="5" t="str">
+      <c r="O43" s="5">
+        <v>999</v>
+      </c>
+      <c r="P43" s="5" t="str">
         <f t="shared" si="8"/>
         <v>SHE999IAN</v>
       </c>
-      <c r="N43" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O43" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P43" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
       <c r="Q43" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Motion 999</v>
       </c>
       <c r="R43" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S43" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T43" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U43" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>55</v>
       </c>
@@ -3701,46 +3901,50 @@
       <c r="D44" t="s">
         <v>87</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="G44" s="12">
+        <v>846</v>
+      </c>
+      <c r="K44" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J44" s="5" t="str">
+      <c r="M44" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K44" s="5">
+      <c r="N44" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L44" s="5">
-        <v>999</v>
-      </c>
-      <c r="M44" s="5" t="str">
+      <c r="O44" s="11">
+        <f>G44</f>
+        <v>846</v>
+      </c>
+      <c r="P44" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>BUR999EMI</v>
-      </c>
-      <c r="N44" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O44" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P44" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+        <v>BUR846EMI</v>
       </c>
       <c r="Q44" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>Kiteboard Motion 999</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="R44" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S44" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T44" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>Motion 846</v>
+      </c>
+      <c r="U44" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>56</v>
       </c>
@@ -3753,49 +3957,52 @@
       <c r="D45" t="s">
         <v>89</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I45" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J45" s="5" t="str">
+      <c r="J45" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M45" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K45" s="5">
+      <c r="N45" s="5">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="L45" s="5">
-        <v>999</v>
-      </c>
-      <c r="M45" s="5" t="str">
+      <c r="O45" s="5">
+        <v>999</v>
+      </c>
+      <c r="P45" s="5" t="str">
         <f t="shared" si="8"/>
         <v>DVO999PAV</v>
       </c>
-      <c r="N45" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O45" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P45" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
       <c r="Q45" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R45" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S45" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T45" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U45" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>57</v>
       </c>
@@ -3808,49 +4015,52 @@
       <c r="D46" t="s">
         <v>91</v>
       </c>
-      <c r="G46" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I46" s="7" t="s">
+      <c r="F46" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L46" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J46" s="5" t="str">
+      <c r="M46" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K46" s="5">
+      <c r="N46" s="5">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="L46" s="5">
-        <v>999</v>
-      </c>
-      <c r="M46" s="5" t="str">
+      <c r="O46" s="5">
+        <v>999</v>
+      </c>
+      <c r="P46" s="5" t="str">
         <f t="shared" si="8"/>
         <v>RUS999ROB</v>
       </c>
-      <c r="N46" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O46" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P46" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
       <c r="Q46" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R46" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>Boat Motion 1999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S46" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="T46" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U46" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Motion 1999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>58</v>
       </c>
@@ -3863,46 +4073,49 @@
       <c r="D47" t="s">
         <v>94</v>
       </c>
-      <c r="G47" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J47" s="5" t="str">
+      <c r="F47" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M47" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K47" s="5">
+      <c r="N47" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L47" s="5">
-        <v>999</v>
-      </c>
-      <c r="M47" s="5" t="str">
+      <c r="O47" s="5">
+        <v>999</v>
+      </c>
+      <c r="P47" s="5" t="str">
         <f t="shared" si="8"/>
         <v>BRA999JAM</v>
       </c>
-      <c r="N47" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O47" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P47" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q47" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R47" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S47" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T47" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U47" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>59</v>
       </c>
@@ -3915,46 +4128,49 @@
       <c r="D48" t="s">
         <v>96</v>
       </c>
-      <c r="G48" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J48" s="5" t="str">
+      <c r="F48" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M48" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K48" s="5">
+      <c r="N48" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L48" s="5">
-        <v>999</v>
-      </c>
-      <c r="M48" s="5" t="str">
+      <c r="O48" s="5">
+        <v>999</v>
+      </c>
+      <c r="P48" s="5" t="str">
         <f t="shared" si="8"/>
         <v>OLI999JOH</v>
       </c>
-      <c r="N48" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O48" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P48" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q48" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R48" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S48" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T48" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U48" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>60</v>
       </c>
@@ -3967,46 +4183,49 @@
       <c r="D49" t="s">
         <v>98</v>
       </c>
-      <c r="G49" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J49" s="5" t="str">
+      <c r="F49" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M49" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K49" s="5">
+      <c r="N49" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L49" s="5">
-        <v>999</v>
-      </c>
-      <c r="M49" s="5" t="str">
+      <c r="O49" s="5">
+        <v>999</v>
+      </c>
+      <c r="P49" s="5" t="str">
         <f t="shared" si="8"/>
         <v>BAR999ANT</v>
       </c>
-      <c r="N49" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O49" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P49" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q49" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R49" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S49" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T49" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U49" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>61</v>
       </c>
@@ -4019,46 +4238,46 @@
       <c r="D50" t="s">
         <v>99</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="L50" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J50" s="5" t="str">
+      <c r="M50" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K50" s="5">
+      <c r="N50" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L50" s="5">
-        <v>999</v>
-      </c>
-      <c r="M50" s="5" t="str">
+      <c r="O50" s="5">
+        <v>999</v>
+      </c>
+      <c r="P50" s="5" t="str">
         <f t="shared" si="8"/>
         <v>MAR999PET</v>
       </c>
-      <c r="N50" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O50" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P50" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
       <c r="Q50" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R50" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v>Boat Motion 999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S50" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T50" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U50" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Motion 999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>63</v>
       </c>
@@ -4071,46 +4290,52 @@
       <c r="D51" t="s">
         <v>100</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J51" s="8">
+      <c r="M51" s="6">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K51" s="5">
+      <c r="N51" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L51" s="5">
-        <v>999</v>
-      </c>
-      <c r="M51" s="5" t="str">
+      <c r="O51" s="5">
+        <v>999</v>
+      </c>
+      <c r="P51" s="5" t="str">
         <f t="shared" si="8"/>
         <v>BER999FIN</v>
       </c>
-      <c r="N51" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O51" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P51" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
       <c r="Q51" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Motion 999</v>
       </c>
       <c r="R51" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S51" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T51" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U51" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>64</v>
       </c>
@@ -4123,46 +4348,49 @@
       <c r="D52" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="F52" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H52" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J52" s="5" t="str">
+      <c r="M52" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K52" s="5">
+      <c r="N52" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L52" s="5">
-        <v>999</v>
-      </c>
-      <c r="M52" s="5" t="str">
+      <c r="O52" s="5">
+        <v>999</v>
+      </c>
+      <c r="P52" s="5" t="str">
         <f t="shared" si="8"/>
         <v>COL999AND</v>
       </c>
-      <c r="N52" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O52" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P52" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
       <c r="Q52" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Motion 999</v>
       </c>
       <c r="R52" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S52" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T52" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U52" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>65</v>
       </c>
@@ -4175,46 +4403,49 @@
       <c r="D53" t="s">
         <v>101</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="F53" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J53" s="5" t="str">
+      <c r="M53" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K53" s="5">
+      <c r="N53" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L53" s="5">
-        <v>999</v>
-      </c>
-      <c r="M53" s="5" t="str">
+      <c r="O53" s="5">
+        <v>999</v>
+      </c>
+      <c r="P53" s="5" t="str">
         <f t="shared" si="8"/>
         <v>COL999ANN</v>
       </c>
-      <c r="N53" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O53" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P53" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
       <c r="Q53" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Motion 999</v>
       </c>
       <c r="R53" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S53" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T53" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U53" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>66</v>
       </c>
@@ -4227,46 +4458,52 @@
       <c r="D54" t="s">
         <v>100</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H54" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J54" s="5" t="str">
+      <c r="M54" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K54" s="5">
+      <c r="N54" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L54" s="5">
-        <v>999</v>
-      </c>
-      <c r="M54" s="5" t="str">
+      <c r="O54" s="5">
+        <v>999</v>
+      </c>
+      <c r="P54" s="5" t="str">
         <f t="shared" si="8"/>
         <v>BER999ARL</v>
       </c>
-      <c r="N54" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O54" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P54" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
       <c r="Q54" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Motion 999</v>
       </c>
       <c r="R54" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S54" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T54" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U54" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>67</v>
       </c>
@@ -4279,49 +4516,52 @@
       <c r="D55" t="s">
         <v>105</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I55" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G55" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J55" s="5" t="str">
+      <c r="J55" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M55" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K55" s="5">
+      <c r="N55" s="5">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="L55" s="5">
-        <v>999</v>
-      </c>
-      <c r="M55" s="5" t="str">
+      <c r="O55" s="5">
+        <v>999</v>
+      </c>
+      <c r="P55" s="5" t="str">
         <f t="shared" si="8"/>
         <v>CON999GAR</v>
       </c>
-      <c r="N55" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O55" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P55" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
       <c r="Q55" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R55" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S55" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T55" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U55" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>68</v>
       </c>
@@ -4334,49 +4574,52 @@
       <c r="D56" t="s">
         <v>106</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I56" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G56" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J56" s="5" t="str">
+      <c r="J56" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M56" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K56" s="5">
+      <c r="N56" s="5">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="L56" s="5">
-        <v>999</v>
-      </c>
-      <c r="M56" s="5" t="str">
+      <c r="O56" s="5">
+        <v>999</v>
+      </c>
+      <c r="P56" s="5" t="str">
         <f t="shared" si="8"/>
         <v>DIN999JAM</v>
       </c>
-      <c r="N56" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O56" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P56" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
       <c r="Q56" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R56" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S56" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T56" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U56" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>69</v>
       </c>
@@ -4389,46 +4632,49 @@
       <c r="D57" t="s">
         <v>108</v>
       </c>
-      <c r="G57" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J57" s="5" t="str">
+      <c r="F57" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M57" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K57" s="5">
+      <c r="N57" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L57" s="5">
-        <v>999</v>
-      </c>
-      <c r="M57" s="5" t="str">
+      <c r="O57" s="5">
+        <v>999</v>
+      </c>
+      <c r="P57" s="5" t="str">
         <f t="shared" si="8"/>
         <v>TRO999WIL</v>
       </c>
-      <c r="N57" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O57" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P57" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q57" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R57" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S57" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T57" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U57" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>70</v>
       </c>
@@ -4441,49 +4687,52 @@
       <c r="D58" t="s">
         <v>110</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="F58" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H58" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H58" s="7" t="s">
+      <c r="K58" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J58" s="5" t="str">
+      <c r="M58" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K58" s="5">
+      <c r="N58" s="5">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="L58" s="5">
-        <v>999</v>
-      </c>
-      <c r="M58" s="5" t="str">
+      <c r="O58" s="5">
+        <v>999</v>
+      </c>
+      <c r="P58" s="5" t="str">
         <f t="shared" si="8"/>
         <v>WIL999DAV</v>
       </c>
-      <c r="N58" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>Wingboard Motion 5999</v>
-      </c>
-      <c r="O58" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P58" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
       <c r="Q58" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>Kiteboard Motion 2999</v>
+        <f t="shared" si="2"/>
+        <v>Motion 5999</v>
       </c>
       <c r="R58" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S58" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T58" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>Motion 2999</v>
+      </c>
+      <c r="U58" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>71</v>
       </c>
@@ -4496,46 +4745,53 @@
       <c r="D59" t="s">
         <v>111</v>
       </c>
-      <c r="G59" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J59" s="5" t="str">
+      <c r="F59" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G59" s="8">
+        <v>920</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M59" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K59" s="5">
+      <c r="N59" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L59" s="5">
-        <v>999</v>
-      </c>
-      <c r="M59" s="5" t="str">
+      <c r="O59" s="11">
+        <f>G59</f>
+        <v>920</v>
+      </c>
+      <c r="P59" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>PAL999MAR</v>
-      </c>
-      <c r="N59" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O59" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P59" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
+        <v>PAL920MAR</v>
       </c>
       <c r="Q59" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R59" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S59" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 920</v>
+      </c>
+      <c r="T59" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U59" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>72</v>
       </c>
@@ -4548,46 +4804,49 @@
       <c r="D60" t="s">
         <v>112</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="F60" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H60" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J60" s="5" t="str">
+      <c r="M60" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K60" s="5">
+      <c r="N60" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L60" s="5">
-        <v>999</v>
-      </c>
-      <c r="M60" s="5" t="str">
+      <c r="O60" s="5">
+        <v>999</v>
+      </c>
+      <c r="P60" s="5" t="str">
         <f t="shared" si="8"/>
         <v>SAN999SIM</v>
       </c>
-      <c r="N60" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O60" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P60" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
       <c r="Q60" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Motion 999</v>
       </c>
       <c r="R60" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S60" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T60" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U60" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>73</v>
       </c>
@@ -4600,49 +4859,52 @@
       <c r="D61" t="s">
         <v>113</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I61" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J61" s="5" t="str">
+      <c r="J61" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M61" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K61" s="5">
+      <c r="N61" s="5">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="L61" s="5">
-        <v>999</v>
-      </c>
-      <c r="M61" s="5" t="str">
+      <c r="O61" s="5">
+        <v>999</v>
+      </c>
+      <c r="P61" s="5" t="str">
         <f t="shared" si="8"/>
         <v>NEW999MAR</v>
       </c>
-      <c r="N61" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O61" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P61" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
       <c r="Q61" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R61" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S61" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T61" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U61" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>75</v>
       </c>
@@ -4655,46 +4917,49 @@
       <c r="D62" t="s">
         <v>115</v>
       </c>
-      <c r="G62" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J62" s="8">
+      <c r="F62" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J62" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M62" s="6">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K62" s="5">
+      <c r="N62" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L62" s="5">
-        <v>999</v>
-      </c>
-      <c r="M62" s="5" t="str">
+      <c r="O62" s="5">
+        <v>999</v>
+      </c>
+      <c r="P62" s="5" t="str">
         <f t="shared" si="8"/>
         <v>MAR999EDD</v>
       </c>
-      <c r="N62" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O62" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P62" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q62" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R62" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S62" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T62" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U62" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>76</v>
       </c>
@@ -4707,46 +4972,49 @@
       <c r="D63" t="s">
         <v>117</v>
       </c>
-      <c r="G63" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J63" s="5" t="str">
+      <c r="F63" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M63" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K63" s="5">
+      <c r="N63" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L63" s="5">
-        <v>999</v>
-      </c>
-      <c r="M63" s="5" t="str">
+      <c r="O63" s="5">
+        <v>999</v>
+      </c>
+      <c r="P63" s="5" t="str">
         <f t="shared" si="8"/>
         <v>STU999AND</v>
       </c>
-      <c r="N63" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O63" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P63" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q63" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R63" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S63" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T63" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U63" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>77</v>
       </c>
@@ -4759,46 +5027,46 @@
       <c r="D64" t="s">
         <v>118</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="K64" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J64" s="5" t="str">
+      <c r="M64" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K64" s="5">
+      <c r="N64" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L64" s="5">
-        <v>999</v>
-      </c>
-      <c r="M64" s="5" t="str">
+      <c r="O64" s="5">
+        <v>999</v>
+      </c>
+      <c r="P64" s="5" t="str">
         <f t="shared" si="8"/>
         <v>LON999JAM</v>
       </c>
-      <c r="N64" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O64" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P64" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
       <c r="Q64" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>Kiteboard Motion 999</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="R64" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S64" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T64" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="U64" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>78</v>
       </c>
@@ -4811,46 +5079,49 @@
       <c r="D65" t="s">
         <v>78</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J65" s="5" t="str">
+      <c r="F65" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J65" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M65" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K65" s="5">
+      <c r="N65" s="5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="L65" s="5">
-        <v>999</v>
-      </c>
-      <c r="M65" s="5" t="str">
+      <c r="O65" s="5">
+        <v>999</v>
+      </c>
+      <c r="P65" s="5" t="str">
         <f t="shared" si="8"/>
         <v>THO999RUS</v>
       </c>
-      <c r="N65" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O65" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P65" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q65" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R65" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S65" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T65" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U65" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>79</v>
       </c>
@@ -4863,46 +5134,49 @@
       <c r="D66" t="s">
         <v>120</v>
       </c>
-      <c r="G66" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J66" s="5" t="str">
+      <c r="F66" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M66" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K66" s="5">
-        <f t="shared" ref="K66:K86" si="15">COUNTA(E66:I66)</f>
+      <c r="N66" s="5">
+        <f t="shared" ref="N66:N86" si="10">COUNTA(H66:L66)</f>
         <v>1</v>
       </c>
-      <c r="L66" s="5">
-        <v>999</v>
-      </c>
-      <c r="M66" s="5" t="str">
+      <c r="O66" s="5">
+        <v>999</v>
+      </c>
+      <c r="P66" s="5" t="str">
         <f t="shared" si="8"/>
         <v>KIR999JON</v>
       </c>
-      <c r="N66" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O66" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P66" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q66" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R66" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S66" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T66" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U66" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>80</v>
       </c>
@@ -4915,46 +5189,49 @@
       <c r="D67" t="s">
         <v>122</v>
       </c>
-      <c r="G67" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J67" s="5" t="str">
+      <c r="F67" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J67" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M67" s="5" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K67" s="5">
-        <f t="shared" si="15"/>
+      <c r="N67" s="5">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="L67" s="5">
-        <v>999</v>
-      </c>
-      <c r="M67" s="5" t="str">
+      <c r="O67" s="5">
+        <v>999</v>
+      </c>
+      <c r="P67" s="5" t="str">
         <f t="shared" si="8"/>
         <v>CRO999JIM</v>
       </c>
-      <c r="N67" s="3" t="str">
-        <f t="shared" ref="N67:N86" si="16">IF(E67&lt;&gt;"", _xlfn.CONCAT(E67, " ",IF(COUNTA($E67:$I67)&gt;1,"5",""),$L67), "")</f>
-        <v/>
-      </c>
-      <c r="O67" s="3" t="str">
-        <f t="shared" ref="O67:O86" si="17">IF(F67&lt;&gt;"", _xlfn.CONCAT(F67, " ",IF(COUNTA($E67:$I67)&gt;1,"4",""),$L67), "")</f>
-        <v/>
-      </c>
-      <c r="P67" s="3" t="str">
-        <f t="shared" ref="P67:P86" si="18">IF(G67&lt;&gt;"", _xlfn.CONCAT(G67, " ",IF(COUNTA($E67:$I67)&gt;1,"3",""),$L67), "")</f>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q67" s="3" t="str">
-        <f t="shared" ref="Q67:Q86" si="19">IF(H67&lt;&gt;"", _xlfn.CONCAT(H67, " ",IF(COUNTA($E67:$I67)&gt;1,"2",""),$L67), "")</f>
+        <f t="shared" ref="Q67:Q86" si="11">IF(H67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"5",""),$O67), "")</f>
         <v/>
       </c>
       <c r="R67" s="3" t="str">
-        <f t="shared" ref="R67:R86" si="20">IF(I67&lt;&gt;"", _xlfn.CONCAT(I67, " ",IF(COUNTA($E67:$I67)&gt;1,"1",""),$L67), "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" ref="R67:R86" si="12">IF(I67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"4",""),$O67), "")</f>
+        <v/>
+      </c>
+      <c r="S67" s="3" t="str">
+        <f t="shared" ref="S67:S86" si="13">IF(J67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF(AND($N67&gt;1,$I67=""),"4",""),$O67), "")</f>
+        <v>Motion 999</v>
+      </c>
+      <c r="T67" s="3" t="str">
+        <f t="shared" ref="T67:T86" si="14">IF(K67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"2",""),$O67), "")</f>
+        <v/>
+      </c>
+      <c r="U67" s="3" t="str">
+        <f t="shared" ref="U67:U86" si="15">IF(L67&lt;&gt;"", _xlfn.CONCAT("Motion ",IF($N67&gt;1,"1",""),$O67), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>81</v>
       </c>
@@ -4967,46 +5244,52 @@
       <c r="D68" t="s">
         <v>122</v>
       </c>
-      <c r="G68" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J68" s="5" t="str">
-        <f t="shared" ref="J68:J86" si="21">IF(A68-A67&lt;&gt;1,A68-A67,"")</f>
-        <v/>
-      </c>
-      <c r="K68" s="5">
-        <f t="shared" si="15"/>
+      <c r="E68" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M68" s="5" t="str">
+        <f t="shared" ref="M68:M86" si="16">IF(A68-A67&lt;&gt;1,A68-A67,"")</f>
+        <v/>
+      </c>
+      <c r="N68" s="5">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="L68" s="5">
-        <v>999</v>
-      </c>
-      <c r="M68" s="5" t="str">
+      <c r="O68" s="5">
+        <v>999</v>
+      </c>
+      <c r="P68" s="5" t="str">
         <f t="shared" si="8"/>
         <v>CRO999GEO</v>
       </c>
-      <c r="N68" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O68" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P68" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q68" s="3" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R68" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S68" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T68" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U68" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>82</v>
       </c>
@@ -5019,46 +5302,52 @@
       <c r="D69" t="s">
         <v>122</v>
       </c>
-      <c r="G69" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J69" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K69" s="5">
-        <f t="shared" si="15"/>
+      <c r="E69" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J69" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M69" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N69" s="5">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="L69" s="5">
-        <v>999</v>
-      </c>
-      <c r="M69" s="5" t="str">
+      <c r="O69" s="5">
+        <v>999</v>
+      </c>
+      <c r="P69" s="5" t="str">
         <f t="shared" si="8"/>
         <v>CRO999JAC</v>
       </c>
-      <c r="N69" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O69" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P69" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
       <c r="Q69" s="3" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R69" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S69" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T69" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U69" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>83</v>
       </c>
@@ -5071,49 +5360,52 @@
       <c r="D70" t="s">
         <v>124</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I70" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J70" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K70" s="5">
-        <f t="shared" si="15"/>
+      <c r="J70" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M70" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N70" s="5">
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="L70" s="5">
-        <v>999</v>
-      </c>
-      <c r="M70" s="5" t="str">
+      <c r="O70" s="5">
+        <v>999</v>
+      </c>
+      <c r="P70" s="5" t="str">
         <f t="shared" si="8"/>
         <v>NOR999SCO</v>
       </c>
-      <c r="N70" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O70" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P70" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
       <c r="Q70" s="3" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R70" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S70" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T70" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U70" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>84</v>
       </c>
@@ -5126,46 +5418,46 @@
       <c r="D71" t="s">
         <v>125</v>
       </c>
-      <c r="H71" s="7" t="s">
+      <c r="K71" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J71" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K71" s="5">
-        <f t="shared" si="15"/>
+      <c r="M71" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N71" s="5">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="L71" s="5">
-        <v>999</v>
-      </c>
-      <c r="M71" s="5" t="str">
+      <c r="O71" s="5">
+        <v>999</v>
+      </c>
+      <c r="P71" s="5" t="str">
         <f t="shared" si="8"/>
         <v>CAM999SEB</v>
       </c>
-      <c r="N71" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O71" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P71" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
       <c r="Q71" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v>Kiteboard Motion 999</v>
+        <f t="shared" si="11"/>
+        <v/>
       </c>
       <c r="R71" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S71" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="T71" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="U71" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>85</v>
       </c>
@@ -5178,46 +5470,49 @@
       <c r="D72" t="s">
         <v>126</v>
       </c>
-      <c r="G72" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J72" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K72" s="5">
+      <c r="F72" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M72" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N72" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O72" s="5">
+        <v>999</v>
+      </c>
+      <c r="P72" s="5" t="str">
+        <f t="shared" ref="P72:P86" si="17">UPPER(_xlfn.CONCAT(LEFT(D72,3),O72,LEFT(C72,3)))</f>
+        <v>HIL999IAN</v>
+      </c>
+      <c r="Q72" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R72" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S72" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T72" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U72" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L72" s="5">
-        <v>999</v>
-      </c>
-      <c r="M72" s="5" t="str">
-        <f t="shared" ref="M72:M86" si="22">UPPER(_xlfn.CONCAT(LEFT(D72,3),L72,LEFT(C72,3)))</f>
-        <v>HIL999IAN</v>
-      </c>
-      <c r="N72" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O72" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P72" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q72" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R72" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>86</v>
       </c>
@@ -5230,49 +5525,52 @@
       <c r="D73" t="s">
         <v>127</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="F73" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I73" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G73" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J73" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K73" s="5">
+      <c r="J73" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M73" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N73" s="5">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="O73" s="5">
+        <v>999</v>
+      </c>
+      <c r="P73" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>TWI999AND</v>
+      </c>
+      <c r="Q73" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R73" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S73" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T73" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U73" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="L73" s="5">
-        <v>999</v>
-      </c>
-      <c r="M73" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>TWI999AND</v>
-      </c>
-      <c r="N73" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O73" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P73" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q73" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R73" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>87</v>
       </c>
@@ -5285,46 +5583,49 @@
       <c r="D74" t="s">
         <v>129</v>
       </c>
-      <c r="G74" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J74" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K74" s="5">
+      <c r="F74" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J74" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M74" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N74" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O74" s="5">
+        <v>999</v>
+      </c>
+      <c r="P74" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>HUM999TIM</v>
+      </c>
+      <c r="Q74" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R74" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S74" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T74" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U74" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L74" s="5">
-        <v>999</v>
-      </c>
-      <c r="M74" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>HUM999TIM</v>
-      </c>
-      <c r="N74" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O74" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P74" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q74" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R74" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>88</v>
       </c>
@@ -5337,46 +5638,53 @@
       <c r="D75" t="s">
         <v>130</v>
       </c>
-      <c r="G75" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J75" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K75" s="5">
+      <c r="F75" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G75" s="8">
+        <v>1002</v>
+      </c>
+      <c r="J75" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M75" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N75" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O75" s="11">
+        <f>G75</f>
+        <v>1002</v>
+      </c>
+      <c r="P75" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>GOO1002GAR</v>
+      </c>
+      <c r="Q75" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R75" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S75" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 1002</v>
+      </c>
+      <c r="T75" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U75" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L75" s="5">
-        <v>999</v>
-      </c>
-      <c r="M75" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>GOO999GAR</v>
-      </c>
-      <c r="N75" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O75" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P75" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q75" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R75" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>89</v>
       </c>
@@ -5389,46 +5697,49 @@
       <c r="D76" t="s">
         <v>132</v>
       </c>
-      <c r="G76" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J76" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K76" s="5">
+      <c r="F76" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J76" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M76" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N76" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O76" s="5">
+        <v>999</v>
+      </c>
+      <c r="P76" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>WHA999TRE</v>
+      </c>
+      <c r="Q76" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R76" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S76" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T76" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U76" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L76" s="5">
-        <v>999</v>
-      </c>
-      <c r="M76" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>WHA999TRE</v>
-      </c>
-      <c r="N76" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O76" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P76" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q76" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R76" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>90</v>
       </c>
@@ -5441,46 +5752,52 @@
       <c r="D77" t="s">
         <v>133</v>
       </c>
-      <c r="G77" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J77" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K77" s="5">
+      <c r="E77" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J77" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M77" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N77" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O77" s="5">
+        <v>999</v>
+      </c>
+      <c r="P77" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>KIE999OLI</v>
+      </c>
+      <c r="Q77" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R77" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S77" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T77" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U77" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L77" s="5">
-        <v>999</v>
-      </c>
-      <c r="M77" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>KIE999OLI</v>
-      </c>
-      <c r="N77" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O77" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P77" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q77" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R77" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>91</v>
       </c>
@@ -5493,46 +5810,53 @@
       <c r="D78" t="s">
         <v>135</v>
       </c>
-      <c r="G78" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J78" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K78" s="5">
+      <c r="F78" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G78" s="8">
+        <v>676</v>
+      </c>
+      <c r="J78" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M78" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N78" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O78" s="11">
+        <f>G78</f>
+        <v>676</v>
+      </c>
+      <c r="P78" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>NEA676IAI</v>
+      </c>
+      <c r="Q78" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R78" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S78" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 676</v>
+      </c>
+      <c r="T78" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U78" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L78" s="5">
-        <v>999</v>
-      </c>
-      <c r="M78" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>NEA999IAI</v>
-      </c>
-      <c r="N78" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O78" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P78" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q78" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R78" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>92</v>
       </c>
@@ -5545,46 +5869,46 @@
       <c r="D79" t="s">
         <v>137</v>
       </c>
-      <c r="H79" s="7" t="s">
+      <c r="K79" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J79" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K79" s="5">
+      <c r="M79" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N79" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O79" s="5">
+        <v>999</v>
+      </c>
+      <c r="P79" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>CAR999MAR</v>
+      </c>
+      <c r="Q79" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R79" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S79" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="T79" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="U79" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L79" s="5">
-        <v>999</v>
-      </c>
-      <c r="M79" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>CAR999MAR</v>
-      </c>
-      <c r="N79" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O79" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P79" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="Q79" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v>Kiteboard Motion 999</v>
-      </c>
-      <c r="R79" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>93</v>
       </c>
@@ -5597,46 +5921,53 @@
       <c r="D80" t="s">
         <v>139</v>
       </c>
-      <c r="G80" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J80" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K80" s="5">
+      <c r="F80" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G80" s="8">
+        <v>704</v>
+      </c>
+      <c r="J80" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M80" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N80" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O80" s="11">
+        <f>G80</f>
+        <v>704</v>
+      </c>
+      <c r="P80" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>VER704SHA</v>
+      </c>
+      <c r="Q80" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R80" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S80" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 704</v>
+      </c>
+      <c r="T80" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U80" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L80" s="5">
-        <v>999</v>
-      </c>
-      <c r="M80" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>VER999SHA</v>
-      </c>
-      <c r="N80" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O80" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P80" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q80" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R80" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>94</v>
       </c>
@@ -5649,46 +5980,49 @@
       <c r="D81" t="s">
         <v>140</v>
       </c>
-      <c r="G81" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J81" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K81" s="5">
+      <c r="F81" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J81" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M81" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N81" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O81" s="5">
+        <v>999</v>
+      </c>
+      <c r="P81" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>BRA999PAU</v>
+      </c>
+      <c r="Q81" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R81" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S81" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T81" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U81" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L81" s="5">
-        <v>999</v>
-      </c>
-      <c r="M81" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>BRA999PAU</v>
-      </c>
-      <c r="N81" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O81" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P81" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q81" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R81" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>96</v>
       </c>
@@ -5701,49 +6035,52 @@
       <c r="D82" t="s">
         <v>142</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="F82" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="I82" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G82" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J82" s="8">
-        <f t="shared" si="21"/>
+      <c r="J82" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M82" s="6">
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K82" s="5">
+      <c r="N82" s="5">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="O82" s="5">
+        <v>999</v>
+      </c>
+      <c r="P82" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>CRO999ALL</v>
+      </c>
+      <c r="Q82" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R82" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="S82" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T82" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U82" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="L82" s="5">
-        <v>999</v>
-      </c>
-      <c r="M82" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>CRO999ALL</v>
-      </c>
-      <c r="N82" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O82" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v>Sailboard (Foil) Motion 4999</v>
-      </c>
-      <c r="P82" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q82" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R82" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>97</v>
       </c>
@@ -5756,46 +6093,52 @@
       <c r="D83" t="s">
         <v>144</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E83" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J83" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K83" s="5">
+      <c r="M83" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N83" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O83" s="5">
+        <v>999</v>
+      </c>
+      <c r="P83" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>MIL999JAY</v>
+      </c>
+      <c r="Q83" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="R83" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S83" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="T83" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U83" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L83" s="5">
-        <v>999</v>
-      </c>
-      <c r="M83" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>MIL999JAY</v>
-      </c>
-      <c r="N83" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v>Wingboard Motion 999</v>
-      </c>
-      <c r="O83" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P83" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="Q83" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R83" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>98</v>
       </c>
@@ -5808,46 +6151,49 @@
       <c r="D84" t="s">
         <v>145</v>
       </c>
-      <c r="G84" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J84" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K84" s="5">
+      <c r="F84" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J84" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M84" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N84" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O84" s="5">
+        <v>999</v>
+      </c>
+      <c r="P84" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>PEN999ROB</v>
+      </c>
+      <c r="Q84" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R84" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S84" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T84" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U84" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L84" s="5">
-        <v>999</v>
-      </c>
-      <c r="M84" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>PEN999ROB</v>
-      </c>
-      <c r="N84" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O84" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P84" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q84" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R84" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>99</v>
       </c>
@@ -5860,49 +6206,52 @@
       <c r="D85" t="s">
         <v>146</v>
       </c>
-      <c r="G85" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H85" s="7" t="s">
+      <c r="F85" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J85" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K85" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J85" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K85" s="5">
+      <c r="M85" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N85" s="5">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="O85" s="5">
+        <v>999</v>
+      </c>
+      <c r="P85" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>DAV999STE</v>
+      </c>
+      <c r="Q85" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R85" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S85" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 4999</v>
+      </c>
+      <c r="T85" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Motion 2999</v>
+      </c>
+      <c r="U85" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="L85" s="5">
-        <v>999</v>
-      </c>
-      <c r="M85" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>DAV999STE</v>
-      </c>
-      <c r="N85" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O85" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P85" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 3999</v>
-      </c>
-      <c r="Q85" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v>Kiteboard Motion 2999</v>
-      </c>
-      <c r="R85" s="3" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>100</v>
       </c>
@@ -5915,47 +6264,53 @@
       <c r="D86" t="s">
         <v>148</v>
       </c>
-      <c r="G86" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J86" s="5" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="K86" s="5">
+      <c r="E86" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J86" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M86" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N86" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="O86" s="5">
+        <v>999</v>
+      </c>
+      <c r="P86" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>VIC999MIT</v>
+      </c>
+      <c r="Q86" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R86" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S86" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Motion 999</v>
+      </c>
+      <c r="T86" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U86" s="3" t="str">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="L86" s="5">
-        <v>999</v>
-      </c>
-      <c r="M86" s="5" t="str">
-        <f t="shared" si="22"/>
-        <v>VIC999MIT</v>
-      </c>
-      <c r="N86" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O86" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P86" s="3" t="str">
-        <f t="shared" si="18"/>
-        <v>Sailboard (Fin) Motion 999</v>
-      </c>
-      <c r="Q86" s="3" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="R86" s="3" t="str">
-        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R86" xr:uid="{F6066FD3-C540-449E-A841-C1FB8B248615}"/>
+  <autoFilter ref="A1:U86" xr:uid="{F6066FD3-C540-449E-A841-C1FB8B248615}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>